--- a/result_tables/model_metrics_default_0530.xlsx
+++ b/result_tables/model_metrics_default_0530.xlsx
@@ -487,10 +487,10 @@
         <v>0.6624080670634428</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6492126216214442</v>
+        <v>0.6559940568600053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6710869549161956</v>
+        <v>0.6696504674819561</v>
       </c>
       <c r="E2" t="n">
         <v>0.9008319655894504</v>
@@ -518,31 +518,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5296453863193273</v>
+        <v>0.6516853351960501</v>
       </c>
       <c r="C3" t="n">
-        <v>0.522824248942332</v>
+        <v>0.6431756276542604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5363084136773507</v>
+        <v>0.6621540950235676</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8161639028807516</v>
+        <v>0.6703378799026544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1722406118023057</v>
+        <v>0.5301906175094168</v>
       </c>
       <c r="G3" t="n">
-        <v>0.887050160836349</v>
+        <v>0.6857659831121834</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1437416650790627</v>
+        <v>0.1566451961015749</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9068429098102688</v>
+        <v>0.9298711919852791</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1567059556570954</v>
+        <v>0.2418389128963399</v>
       </c>
     </row>
     <row r="4">
@@ -555,10 +555,10 @@
         <v>0.6203277581891766</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6153149938970492</v>
+        <v>0.6115381952808276</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6298665949168263</v>
+        <v>0.6283582987396069</v>
       </c>
       <c r="E4" t="n">
         <v>0.7436187673326164</v>
@@ -589,10 +589,10 @@
         <v>0.6792793907155239</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6664937125201126</v>
+        <v>0.6692154101078011</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6876997510224711</v>
+        <v>0.6883469959214493</v>
       </c>
       <c r="E5" t="n">
         <v>0.9020657648989756</v>
@@ -623,10 +623,10 @@
         <v>0.6831023648620584</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6762675733914276</v>
+        <v>0.672392259831887</v>
       </c>
       <c r="D6" t="n">
-        <v>0.689491657784138</v>
+        <v>0.6907152895421144</v>
       </c>
       <c r="E6" t="n">
         <v>0.9023261078725451</v>
@@ -657,10 +657,10 @@
         <v>0.6651816288094966</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6586832538623524</v>
+        <v>0.6578152412464071</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6713114615798087</v>
+        <v>0.6765382704421946</v>
       </c>
       <c r="E7" t="n">
         <v>0.9003905144603543</v>
@@ -691,10 +691,10 @@
         <v>0.6330284173857466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6246965336420532</v>
+        <v>0.6297987998619871</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6371268436705766</v>
+        <v>0.6401405969985754</v>
       </c>
       <c r="E8" t="n">
         <v>0.9008319655894504</v>
@@ -725,10 +725,10 @@
         <v>0.669828227201491</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6641759946076874</v>
+        <v>0.6614254401203442</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6768715468670585</v>
+        <v>0.6771310991668871</v>
       </c>
       <c r="E9" t="n">
         <v>0.9015903559907182</v>
@@ -759,10 +759,10 @@
         <v>0.6302028437958425</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6178414732788958</v>
+        <v>0.6211386092326731</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6401058779787637</v>
+        <v>0.6343588832426975</v>
       </c>
       <c r="E10" t="n">
         <v>0.9013752900560303</v>
@@ -793,10 +793,10 @@
         <v>0.6707301248652564</v>
       </c>
       <c r="C11" t="n">
-        <v>0.662251315511944</v>
+        <v>0.6602712425193783</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6761334498661363</v>
+        <v>0.6778993053128527</v>
       </c>
       <c r="E11" t="n">
         <v>0.9021789574961797</v>
@@ -888,10 +888,10 @@
         <v>0.6686679498395911</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6627116663713464</v>
+        <v>0.6602711456989846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6751243361589331</v>
+        <v>0.672893699312081</v>
       </c>
       <c r="E2" t="n">
         <v>0.88941934304902</v>
@@ -919,31 +919,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6487363888536324</v>
+        <v>0.6515040109206125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6440329551997992</v>
+        <v>0.645227852675056</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6559513137023548</v>
+        <v>0.6591134290276779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8898914218709549</v>
+        <v>0.6339942436840422</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01101928374655647</v>
+        <v>0.5826446280991735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9991353776088483</v>
+        <v>0.6403770096050131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6130268199233716</v>
+        <v>0.167627652618439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8904427303868836</v>
+        <v>0.9250602856612873</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02164941478925648</v>
+        <v>0.2603517518349259</v>
       </c>
     </row>
     <row r="4">
@@ -956,10 +956,10 @@
         <v>0.6210500711356677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6163822099598963</v>
+        <v>0.6153410411214821</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6298012778446924</v>
+        <v>0.6286511899988433</v>
       </c>
       <c r="E4" t="n">
         <v>0.7312500951771819</v>
@@ -990,10 +990,10 @@
         <v>0.6848602418428751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6795490278419867</v>
+        <v>0.6792944446003553</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6894286233684689</v>
+        <v>0.6932949948835452</v>
       </c>
       <c r="E5" t="n">
         <v>0.8900893904091858</v>
@@ -1024,10 +1024,10 @@
         <v>0.6944149698602582</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6901093816709608</v>
+        <v>0.6896453481282164</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7000909771985235</v>
+        <v>0.701305776907995</v>
       </c>
       <c r="E6" t="n">
         <v>0.8907213668966147</v>
@@ -1058,10 +1058,10 @@
         <v>0.6694906101697025</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6658520619510839</v>
+        <v>0.6625659955806602</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6760070278166828</v>
+        <v>0.6776083292115185</v>
       </c>
       <c r="E7" t="n">
         <v>0.8889396500525378</v>
@@ -1092,10 +1092,10 @@
         <v>0.6393012462396366</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6344294647558898</v>
+        <v>0.6329576496359007</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6453651113008797</v>
+        <v>0.6450018398565024</v>
       </c>
       <c r="E8" t="n">
         <v>0.8894421855726621</v>
@@ -1126,10 +1126,10 @@
         <v>0.6816554136403232</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6768207218616097</v>
+        <v>0.6760080789707242</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6914684143998099</v>
+        <v>0.6885538107813899</v>
       </c>
       <c r="E9" t="n">
         <v>0.8897695950781975</v>
@@ -1160,10 +1160,10 @@
         <v>0.6412644340740697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6346208671757839</v>
+        <v>0.6370329371524318</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6452099074404225</v>
+        <v>0.6470991183114042</v>
       </c>
       <c r="E10" t="n">
         <v>0.8897086816818188</v>
@@ -1194,10 +1194,10 @@
         <v>0.6880531288090916</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6804773300821968</v>
+        <v>0.6830682910973491</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6956639829567541</v>
+        <v>0.6955663948124876</v>
       </c>
       <c r="E11" t="n">
         <v>0.8905843117547627</v>
@@ -1289,10 +1289,10 @@
         <v>0.6683520329769145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6646067202899624</v>
+        <v>0.66131393304163</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6756547502319044</v>
+        <v>0.6755408986273708</v>
       </c>
       <c r="E2" t="n">
         <v>0.8894497997472094</v>
@@ -1320,31 +1320,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5276181072228926</v>
+        <v>0.6484414236901583</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5219429472092089</v>
+        <v>0.6425587484932066</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5300674800421896</v>
+        <v>0.6574966329034324</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7993665006776616</v>
+        <v>0.645027182603134</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1787190082644628</v>
+        <v>0.5710743801652892</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8765130891845155</v>
+        <v>0.6542195284811751</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1524676850763807</v>
+        <v>0.170322898693616</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8956820686879997</v>
+        <v>0.9246460980036297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1645529486366519</v>
+        <v>0.2623884564268084</v>
       </c>
     </row>
     <row r="4">
@@ -1357,10 +1357,10 @@
         <v>0.6207017990291458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6153554195762067</v>
+        <v>0.6133577214167081</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6264275426675076</v>
+        <v>0.6254827467524536</v>
       </c>
       <c r="E4" t="n">
         <v>0.7286079766092558</v>
@@ -1391,10 +1391,10 @@
         <v>0.6839180132070286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6782912351640812</v>
+        <v>0.6790277327590011</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6898216816840947</v>
+        <v>0.6892997111903625</v>
       </c>
       <c r="E5" t="n">
         <v>0.8901655321546591</v>
@@ -1425,10 +1425,10 @@
         <v>0.6906386446636622</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6859295774435387</v>
+        <v>0.6851417912801908</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6946339949537514</v>
+        <v>0.6995499451194904</v>
       </c>
       <c r="E6" t="n">
         <v>0.8906985243729727</v>
@@ -1459,10 +1459,10 @@
         <v>0.6682672277361561</v>
       </c>
       <c r="C7" t="n">
-        <v>0.657519735765501</v>
+        <v>0.6625477123569468</v>
       </c>
       <c r="D7" t="n">
-        <v>0.673429571067527</v>
+        <v>0.6734637661340465</v>
       </c>
       <c r="E7" t="n">
         <v>0.8889548784016325</v>
@@ -1493,10 +1493,10 @@
         <v>0.6390526174831586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6322378483939841</v>
+        <v>0.6319534026024947</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6430897256608383</v>
+        <v>0.6445481322961142</v>
       </c>
       <c r="E8" t="n">
         <v>0.8894345713981148</v>
@@ -1527,10 +1527,10 @@
         <v>0.6749385878853063</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6690220556752655</v>
+        <v>0.6696171889577642</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6832411901350576</v>
+        <v>0.6815333842681051</v>
       </c>
       <c r="E9" t="n">
         <v>0.8895792407145141</v>
@@ -1561,10 +1561,10 @@
         <v>0.640639606848796</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6370597362152526</v>
+        <v>0.634361580811137</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6494019487479927</v>
+        <v>0.6463675376427452</v>
       </c>
       <c r="E10" t="n">
         <v>0.8896858391581769</v>
@@ -1595,10 +1595,10 @@
         <v>0.6834934292660211</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6780895262235355</v>
+        <v>0.6763630845210651</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6913770971979979</v>
+        <v>0.6908893281775215</v>
       </c>
       <c r="E11" t="n">
         <v>0.8903635006928898</v>
